--- a/AAII_Financials/Quarterly/PRVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="92">
   <si>
     <t>PRVA</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>632600</v>
+      </c>
+      <c r="E8" s="3">
         <v>603800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>541200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>580400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>521200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>480100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>460900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>437900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>422300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>415200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>440800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>417300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>413400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>386300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>364400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>342900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>335500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>313800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>275300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>251500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>225800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>213600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>213700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>207200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>183300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>212900</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>569800</v>
+      </c>
+      <c r="E9" s="3">
         <v>543500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>491500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>516600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>470900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>434300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>412900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>392600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>379600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>374400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>401800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>375500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>371900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>347000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>327700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>309000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>301700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>283500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>250400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>225400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>238700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>188100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>190300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>185700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>165900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>192700</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E10" s="3">
         <v>60300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>49700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>63800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>50200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>45800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>48000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>45400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>42700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>40900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>39000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>41700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>41400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>39300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>36700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>33900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>33800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>30300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>24900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>26100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-12900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>25500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>23400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>21500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>17400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>20200</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1070,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1156,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1286,8 +1306,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1328,28 +1348,31 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E15" s="3">
         <v>3300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1900</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1800</v>
       </c>
       <c r="J15" s="3">
         <v>1800</v>
@@ -1364,58 +1387,61 @@
         <v>1800</v>
       </c>
       <c r="N15" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="O15" s="3">
         <v>1700</v>
       </c>
       <c r="P15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q15" s="3">
         <v>1300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1100</v>
-      </c>
-      <c r="R15" s="3">
-        <v>1200</v>
       </c>
       <c r="S15" s="3">
         <v>1200</v>
       </c>
       <c r="T15" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="U15" s="3">
         <v>1100</v>
       </c>
       <c r="V15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W15" s="3">
         <v>500</v>
-      </c>
-      <c r="W15" s="3">
-        <v>400</v>
       </c>
       <c r="X15" s="3">
         <v>400</v>
       </c>
       <c r="Y15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Z15" s="3">
         <v>500</v>
       </c>
       <c r="AA15" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB15" s="3">
         <v>600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>300</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>620900</v>
+      </c>
+      <c r="E17" s="3">
         <v>596400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>529900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>566000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>517800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>474900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>455700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>432100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>417200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>414400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>439400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>411700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>406400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>379600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>362200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>347500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>340800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>325300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>294700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>264300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>418900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>205700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>209500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>198600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>177100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>206400</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E18" s="3">
         <v>7400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>11300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>14400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>5200</v>
       </c>
       <c r="I18" s="3">
         <v>5200</v>
       </c>
       <c r="J18" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K18" s="3">
         <v>5800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-11500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-19400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-12800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-193100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6500</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,13 +1680,14 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-3300</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
@@ -1691,15 +1725,15 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1727,100 +1761,106 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
+      <c r="AC20" s="3">
+        <v>0</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E21" s="3">
         <v>10700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>13900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>7100</v>
       </c>
       <c r="I21" s="3">
         <v>7100</v>
       </c>
       <c r="J21" s="3">
+        <v>7100</v>
+      </c>
+      <c r="K21" s="3">
         <v>7600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-10400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-18200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-12300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-192700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9000</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>6800</v>
       </c>
       <c r="AB21" s="3">
         <v>6800</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
+      <c r="AC21" s="3">
+        <v>6800</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1869,17 +1909,17 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3">
         <v>700</v>
-      </c>
-      <c r="T22" s="3">
-        <v>200</v>
       </c>
       <c r="U22" s="3">
         <v>200</v>
       </c>
       <c r="V22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W22" s="3">
         <v>300</v>
@@ -1888,10 +1928,10 @@
         <v>300</v>
       </c>
       <c r="Y22" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z22" s="3">
         <v>400</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>500</v>
       </c>
       <c r="AA22" s="3">
         <v>500</v>
@@ -1899,186 +1939,195 @@
       <c r="AB22" s="3">
         <v>500</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
+      <c r="AC22" s="3">
+        <v>500</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E23" s="3">
         <v>9300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>16700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>8000</v>
       </c>
       <c r="J23" s="3">
         <v>8000</v>
       </c>
       <c r="K23" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L23" s="3">
         <v>8100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-19500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-193500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>7600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6000</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E24" s="3">
         <v>5600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-13400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-7600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-20000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E26" s="3">
         <v>3700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5900</v>
-      </c>
-      <c r="O26" s="3">
-        <v>6400</v>
       </c>
       <c r="P26" s="3">
         <v>6400</v>
       </c>
       <c r="Q26" s="3">
+        <v>6400</v>
+      </c>
+      <c r="R26" s="3">
         <v>16800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-173500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>16600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5300</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4400</v>
-      </c>
-      <c r="J27" s="3">
-        <v>3500</v>
       </c>
       <c r="K27" s="3">
         <v>3500</v>
       </c>
       <c r="L27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M27" s="3">
         <v>3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5600</v>
-      </c>
-      <c r="O27" s="3">
-        <v>7300</v>
       </c>
       <c r="P27" s="3">
         <v>7300</v>
       </c>
       <c r="Q27" s="3">
+        <v>7300</v>
+      </c>
+      <c r="R27" s="3">
         <v>17800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-17500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-172500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>16700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5400</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,13 +2746,16 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>3300</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
@@ -2723,15 +2793,15 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2759,100 +2829,106 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
+      <c r="AC32" s="3">
+        <v>0</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4400</v>
-      </c>
-      <c r="J33" s="3">
-        <v>3500</v>
       </c>
       <c r="K33" s="3">
         <v>3500</v>
       </c>
       <c r="L33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M33" s="3">
         <v>3000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5600</v>
-      </c>
-      <c r="O33" s="3">
-        <v>7300</v>
       </c>
       <c r="P33" s="3">
         <v>7300</v>
       </c>
       <c r="Q33" s="3">
+        <v>7300</v>
+      </c>
+      <c r="R33" s="3">
         <v>17800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-17500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-172500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>16700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5400</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4400</v>
-      </c>
-      <c r="J35" s="3">
-        <v>3500</v>
       </c>
       <c r="K35" s="3">
         <v>3500</v>
       </c>
       <c r="L35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M35" s="3">
         <v>3000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5600</v>
-      </c>
-      <c r="O35" s="3">
-        <v>7300</v>
       </c>
       <c r="P35" s="3">
         <v>7300</v>
       </c>
       <c r="Q35" s="3">
+        <v>7300</v>
+      </c>
+      <c r="R35" s="3">
         <v>17800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-17500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-172500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>16700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5400</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,77 +3264,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>412200</v>
+      </c>
+      <c r="E41" s="3">
         <v>419500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>479700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>441400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>390100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>469300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>491100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>422000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>387400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>351100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>389500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>330400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>317900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>311200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>348000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>316900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>292200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>315900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>320600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>362100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>299800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>81900</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3264,8 +3351,11 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3350,77 +3440,80 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>574200</v>
+      </c>
+      <c r="E43" s="3">
         <v>513700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>400900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>499000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>444000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>388700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>316200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>409000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>370100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>346100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>290800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>350100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>319800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>260900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>189600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>246300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>213900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>166200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>117400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>98400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>126900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>116700</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3436,8 +3529,11 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3480,8 +3576,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3522,8 +3618,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3566,33 +3665,33 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>14400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6000</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,77 +3707,80 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1025300</v>
+      </c>
+      <c r="E46" s="3">
         <v>966000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>911000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>970900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>883000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>886500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>834800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>853800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>779700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>728100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>700800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>697700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>654000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>588800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>552000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>579600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>521300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>492600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>446700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>469400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>436500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>204600</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3694,8 +3796,11 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3738,8 +3843,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3780,77 +3885,80 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E48" s="3">
         <v>8700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10400</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,77 +3974,80 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>434400</v>
+      </c>
+      <c r="E49" s="3">
         <v>422600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>425800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>339800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>342400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>249700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>251400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>242500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>244000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>245600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>246400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>242900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>231300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>232700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>184300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>185200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>186000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>186900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>187700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>124200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>124300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>124500</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,8 +4241,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4133,68 +4253,68 @@
         <v>20600</v>
       </c>
       <c r="E52" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F52" s="3">
         <v>21000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6900</v>
-      </c>
-      <c r="O52" s="3">
-        <v>4700</v>
       </c>
       <c r="P52" s="3">
         <v>4700</v>
       </c>
       <c r="Q52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="R52" s="3">
         <v>45100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>24900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>30300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>37900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>28800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8800</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,77 +4419,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1488600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1417900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1369400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1351000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1272500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1183500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1135800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1145600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1077600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1031600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>999900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>992300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>937600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>875300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>792800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>807800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>745000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>723200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>686400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>632100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>597100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>348300</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4382,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,77 +4576,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E57" s="3">
         <v>10600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3800</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,8 +4663,11 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4541,19 +4675,19 @@
         <v>2100</v>
       </c>
       <c r="E58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F58" s="3">
         <v>2200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2600</v>
       </c>
       <c r="J58" s="3">
         <v>2600</v>
@@ -4562,23 +4696,23 @@
         <v>2600</v>
       </c>
       <c r="L58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M58" s="3">
         <v>2900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>3200</v>
       </c>
       <c r="O58" s="3">
         <v>3200</v>
       </c>
       <c r="P58" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Q58" s="3">
         <v>3000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4586,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>900</v>
@@ -4595,14 +4729,14 @@
         <v>900</v>
       </c>
       <c r="W58" s="3">
+        <v>900</v>
+      </c>
+      <c r="X58" s="3">
         <v>1300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4618,8 +4752,11 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4662,33 +4799,33 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>257500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>299300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>258600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>211000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>186600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>183100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>161500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>152600</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,77 +4841,80 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>634400</v>
+      </c>
+      <c r="E60" s="3">
         <v>601300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>568500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>582900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>534900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>470800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>449100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>479500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>429600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>403800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>387000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>394200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>358400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>309700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>264300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>304500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>265100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>220400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>190500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>187200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>167300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>157500</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,53 +4930,56 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E61" s="3">
         <v>6900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4100</v>
-      </c>
-      <c r="H61" s="3">
-        <v>3000</v>
       </c>
       <c r="I61" s="3">
         <v>3000</v>
       </c>
       <c r="J61" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K61" s="3">
         <v>3600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4844,23 +4987,23 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>31500</v>
-      </c>
-      <c r="U61" s="3">
-        <v>31700</v>
       </c>
       <c r="V61" s="3">
         <v>31700</v>
       </c>
       <c r="W61" s="3">
+        <v>31700</v>
+      </c>
+      <c r="X61" s="3">
         <v>31900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>32300</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4876,31 +5019,34 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E62" s="3">
         <v>3500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3">
-        <v>200</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I62" s="3">
         <v>200</v>
       </c>
       <c r="J62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K62" s="3">
         <v>300</v>
@@ -4912,7 +5058,7 @@
         <v>300</v>
       </c>
       <c r="N62" s="3">
-        <v>1300</v>
+        <v>300</v>
       </c>
       <c r="O62" s="3">
         <v>1300</v>
@@ -4921,32 +5067,32 @@
         <v>1300</v>
       </c>
       <c r="Q62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R62" s="3">
         <v>9500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>14000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9100</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,77 +5375,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>650500</v>
+      </c>
+      <c r="E66" s="3">
         <v>612000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>578400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>588200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>539000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>474000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>452300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>483400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>434000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>408800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>392500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>401300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>366300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>318800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>293700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>337600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>299800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>288100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>259500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>221500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>203800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>196000</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5306,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,77 +5853,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-144200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-153200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-156300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-165500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-172300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-175000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-179200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-183600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-187200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-190600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-193600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-196500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-202100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-209400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-216700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-234500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-236100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-225600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-208100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-196100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-187000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-14500</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5768,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,77 +6209,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>782300</v>
+      </c>
+      <c r="E76" s="3">
         <v>753100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>737200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>709100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>682900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>659400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>635200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>614900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>595400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>576800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>561400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>544700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>525200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>513300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>499100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>470200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>445200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>435000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>426900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>410600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>393300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>152200</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6112,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4400</v>
-      </c>
-      <c r="J81" s="3">
-        <v>3500</v>
       </c>
       <c r="K81" s="3">
         <v>3500</v>
       </c>
       <c r="L81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M81" s="3">
         <v>3000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5600</v>
-      </c>
-      <c r="O81" s="3">
-        <v>7300</v>
       </c>
       <c r="P81" s="3">
         <v>7300</v>
       </c>
       <c r="Q81" s="3">
+        <v>7300</v>
+      </c>
+      <c r="R81" s="3">
         <v>17800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-17500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-172500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>16700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5400</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6419,7 +6618,7 @@
         <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>300</v>
@@ -6452,49 +6651,52 @@
         <v>300</v>
       </c>
       <c r="Q83" s="3">
+        <v>300</v>
+      </c>
+      <c r="R83" s="3">
         <v>1100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1200</v>
       </c>
       <c r="S83" s="3">
         <v>1200</v>
       </c>
       <c r="T83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="U83" s="3">
         <v>1100</v>
       </c>
       <c r="V83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W83" s="3">
         <v>500</v>
-      </c>
-      <c r="W83" s="3">
-        <v>400</v>
       </c>
       <c r="X83" s="3">
         <v>400</v>
       </c>
       <c r="Y83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Z83" s="3">
         <v>500</v>
       </c>
       <c r="AA83" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB83" s="3">
         <v>600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>300</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-49500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>127500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>52000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-24100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>74800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>33200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>34500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-33100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>64100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>22500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>29200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>16100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-12300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>62700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>35500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>13800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,8 +7261,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7085,8 +7306,8 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7098,37 +7319,40 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>-200</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-400</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
+      <c r="AC91" s="3">
+        <v>0</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,53 +7526,56 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-11500</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-91300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-89100</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>-6300</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-5700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-24900</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -7356,16 +7586,16 @@
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-32400</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-200</v>
       </c>
       <c r="W94" s="3">
         <v>-200</v>
       </c>
       <c r="X94" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -7374,19 +7604,22 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-400</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
+      <c r="AC94" s="3">
+        <v>0</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7461,8 +7695,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,94 +8004,100 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>3000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>8600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-30900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>210800</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-200</v>
       </c>
       <c r="Y100" s="3">
         <v>-200</v>
       </c>
       <c r="Z100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>10000</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7891,8 +8140,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7933,90 +8182,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-60200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>38300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>51200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-79200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>69200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>34600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>36200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-38400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>59100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>12400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>31100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>24700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-23700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-41500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>62400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>217800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>25400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2900</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
